--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N44_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N44_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.12702238160676</v>
+        <v>7.170641137011098</v>
       </c>
       <c r="D2" t="n">
-        <v>27.22938134844166</v>
+        <v>4.42477446912177</v>
       </c>
       <c r="E2" t="n">
-        <v>17.03510414326132</v>
+        <v>2.768204423279964</v>
       </c>
       <c r="F2" t="n">
-        <v>16.4830274584051</v>
+        <v>2.678491961990829</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.31444245313828</v>
+        <v>6.06359689863497</v>
       </c>
       <c r="D3" t="n">
-        <v>30.62752327993779</v>
+        <v>4.97697253298989</v>
       </c>
       <c r="E3" t="n">
-        <v>17.03510414326132</v>
+        <v>2.768204423279964</v>
       </c>
       <c r="F3" t="n">
-        <v>16.4830274584051</v>
+        <v>2.678491961990829</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.43211520224244</v>
+        <v>4.132718720364396</v>
       </c>
       <c r="D4" t="n">
-        <v>33.76028649825776</v>
+        <v>5.486046555966886</v>
       </c>
       <c r="E4" t="n">
-        <v>17.03510414326132</v>
+        <v>2.768204423279964</v>
       </c>
       <c r="F4" t="n">
-        <v>16.4830274584051</v>
+        <v>2.678491961990829</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>10.452148336313</v>
+        <v>1.698474104650863</v>
       </c>
       <c r="D5" t="n">
-        <v>13.60785108351466</v>
+        <v>2.211275801071133</v>
       </c>
       <c r="E5" t="n">
-        <v>17.03510414326132</v>
+        <v>2.768204423279964</v>
       </c>
       <c r="F5" t="n">
-        <v>16.4830274584051</v>
+        <v>2.678491961990829</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>62.68547158840554</v>
+        <v>10.1863891331159</v>
       </c>
       <c r="D6" t="n">
-        <v>62.60343822945628</v>
+        <v>10.17305871228665</v>
       </c>
       <c r="E6" t="n">
-        <v>17.03510414326132</v>
+        <v>2.768204423279964</v>
       </c>
       <c r="F6" t="n">
-        <v>16.4830274584051</v>
+        <v>2.678491961990829</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>51.35820468636686</v>
+        <v>8.345708261534615</v>
       </c>
       <c r="D7" t="n">
-        <v>51.20017493031838</v>
+        <v>8.320028426176737</v>
       </c>
       <c r="E7" t="n">
-        <v>17.03510414326132</v>
+        <v>2.768204423279964</v>
       </c>
       <c r="F7" t="n">
-        <v>16.4830274584051</v>
+        <v>2.678491961990829</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>56.97427219118655</v>
+        <v>9.258319231067814</v>
       </c>
       <c r="D8" t="n">
-        <v>56.78004821200528</v>
+        <v>9.22675783445086</v>
       </c>
       <c r="E8" t="n">
-        <v>17.03510414326132</v>
+        <v>2.768204423279964</v>
       </c>
       <c r="F8" t="n">
-        <v>16.4830274584051</v>
+        <v>2.678491961990829</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
